--- a/per-stock/BTDR/financials.xlsx
+++ b/per-stock/BTDR/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3248237312</v>
+        <v>4362613760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4879009792</v>
+        <v>5947949568</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-65.65681499999999</v>
+        <v>-88.18178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3951225</v>
+        <v>5.902962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-736072640</v>
+        <v>-2117299000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.35</v>
+        <v>17.93</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B35:E35)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B9:E9)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -842,10 +1322,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25503690.060709</v>
+        <v>25510206.1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-2038520.28112</v>
+        <v>-2058159</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>728070</v>
@@ -862,10 +1342,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.073881</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.004061</v>
+        <v>0.0041</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.21</v>
@@ -1102,10 +1582,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-254098309.939291</v>
+        <v>-254091793.9</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-99199520.28112</v>
+        <v>-99219159</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>-59394930</v>
@@ -1920,13 +2400,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1935,6 +2415,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1945,25 +2426,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
@@ -1976,7 +2462,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>-13514.278174</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -1988,8 +2474,9 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>43387470</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1998,20 +2485,21 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.020952</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.032545</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.001332</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.001429</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2020,819 +2508,958 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-132780000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>275900000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>6858000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>376297000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-86810000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>-542582000</v>
-      </c>
+        <v>-102615000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Net Income From Continuing Operation Net Minority Interest</t>
+          <t>Total Unusual Items</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>70542000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-266685000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>-147733000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>409473000</v>
-      </c>
+        <v>-645000</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>206607000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reconciled Cost Of Revenue</t>
+          <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>214265000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>128881000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>142762000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>73353000</v>
-      </c>
+        <v>-645000</v>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
-        <v>63919000</v>
-      </c>
+        <v>206607000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>275900000</v>
+        <v>-159527000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6858000</v>
+        <v>70542000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>376297000</v>
+        <v>-266685000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-86810000</v>
+        <v>-147733000</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-542582000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>275900000</v>
+        <v>227971000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6858000</v>
+        <v>214265000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>376297000</v>
+        <v>128881000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-86810000</v>
+        <v>142762000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-542582000</v>
-      </c>
+        <v>74098000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net Interest Income</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-39880000</v>
+        <v>-133425000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-29416000</v>
+        <v>275900000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-17141000</v>
+        <v>6858000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-9343000</v>
+        <v>376297000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-10226000</v>
-      </c>
+        <v>103992000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Normalized Income</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>70542000</v>
+        <v>-133425000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-266685000</v>
+        <v>275900000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-147733000</v>
+        <v>6858000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>409473000</v>
+        <v>376297000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>103992000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Net Income From Continuing And Discontinued Operation</t>
+          <t>Net Interest Income</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>70542000</v>
+        <v>-29516000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-266685000</v>
+        <v>-39880000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-147733000</v>
+        <v>-29416000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>409473000</v>
+        <v>-17141000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>-5290000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>303666000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>162850000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>180482000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>156938000</v>
-      </c>
+        <v>29516000</v>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n">
-        <v>117299000</v>
-      </c>
+        <v>5290000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total Operating Income As Reported</t>
+          <t>Normalized Income</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>109353000</v>
+        <v>-158895514.278174</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-231636000</v>
+        <v>70542000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-134237000</v>
+        <v>-266685000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>416240000</v>
+        <v>-147733000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-520867000</v>
-      </c>
+        <v>-57904530</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Diluted Average Shares</t>
+          <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>268150000</v>
+        <v>-159527000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>208619000</v>
+        <v>70542000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>193970000</v>
+        <v>-266685000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>228561000</v>
+        <v>-147733000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>165427000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Basic Average Shares</t>
+          <t>Total Expenses</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>225305000</v>
+        <v>294862000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>208619000</v>
+        <v>303666000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>193970000</v>
+        <v>162850000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>190199000</v>
+        <v>180482000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>165427000</v>
-      </c>
+        <v>168594000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Diluted EPS</t>
+          <t>Total Operating Income As Reported</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.73</v>
+        <v>-105932000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.28</v>
+        <v>109353000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.76</v>
+        <v>-231636000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.37</v>
+        <v>-134237000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-3.22</v>
-      </c>
+        <v>-98466000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Basic EPS</t>
+          <t>Diluted Average Shares</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.31</v>
+        <v>233393000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-1.28</v>
+        <v>268150000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.76</v>
+        <v>208619000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.15</v>
+        <v>193970000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-3.22</v>
-      </c>
+        <v>203476000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Diluted NI Availto Com Stockholders</t>
+          <t>Basic Average Shares</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-331236000</v>
+        <v>233393000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-266685000</v>
+        <v>225305000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-542657000</v>
+        <v>208619000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>409473000</v>
+        <v>193970000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>190199000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net Income Common Stockholders</t>
+          <t>Diluted EPS</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>70542000</v>
+        <v>-0.68</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-266685000</v>
+        <v>-0.73</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-147733000</v>
+        <v>-1.28</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>409473000</v>
+        <v>-0.76</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>-0.47</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Basic EPS</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>70542000</v>
+        <v>-0.68</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-266685000</v>
+        <v>0.31</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-147733000</v>
+        <v>-1.28</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>409473000</v>
+        <v>-0.76</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>0.55</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>70542000</v>
+        <v>-159527000</v>
       </c>
       <c r="C21" s="3" t="n">
+        <v>-331236000</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>-266685000</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>-147733000</v>
-      </c>
       <c r="E21" s="3" t="n">
-        <v>409473000</v>
+        <v>-542657000</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
+          <t>Net Income Common Stockholders</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-159527000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>70542000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-266685000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-147733000</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>409473000</v>
-      </c>
       <c r="F22" s="3" t="n">
-        <v>-531917000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2373000</v>
+        <v>-159527000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5633000</v>
+        <v>70542000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-197000</v>
+        <v>-266685000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-2576000</v>
+        <v>-147733000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-761000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>72915000</v>
+        <v>-159527000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-261052000</v>
+        <v>70542000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-147930000</v>
+        <v>-266685000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>406897000</v>
+        <v>-147733000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-532678000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>191626000</v>
+        <v>-159527000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-238494000</v>
+        <v>70542000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-105889000</v>
+        <v>-266685000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>503050000</v>
+        <v>-147733000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-474171000</v>
-      </c>
+        <v>105315000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-153573000</v>
+        <v>-3414000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-238494000</v>
+        <v>2373000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-504901000</v>
+        <v>5633000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>503050000</v>
+        <v>-197000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>27819000</v>
-      </c>
+        <v>-6613000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-39880000</v>
+        <v>-162941000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-29416000</v>
+        <v>72915000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-17141000</v>
+        <v>-261052000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-9343000</v>
+        <v>-147930000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10226000</v>
-      </c>
+        <v>98702000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Total Other Finance Cost</t>
+          <t>Other Income Expense</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-51847000</v>
+        <v>-27493000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>29416000</v>
+        <v>191626000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-9191000</v>
+        <v>-238494000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>9343000</v>
+        <v>-105889000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>176000</v>
-      </c>
+        <v>202458000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-78831000</v>
+        <v>-24961000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6858000</v>
+        <v>-153573000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-24900000</v>
+        <v>-238494000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-86810000</v>
+        <v>-504901000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-48281000</v>
-      </c>
+        <v>-1453000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Earnings From Equity Interest</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>89401000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>33969000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>37720000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>83585000</v>
-      </c>
+        <v>-1887000</v>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n">
-        <v>53380000</v>
-      </c>
+        <v>-2696000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Other Operating Expenses</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>23060000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>-26511000</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>-4621000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>7789000</v>
-      </c>
+        <v>-645000</v>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>10862000</v>
-      </c>
+        <v>206607000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Research And Development</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>35197000</v>
+        <v>-29516000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>39088000</v>
+        <v>-39880000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20577000</v>
+        <v>-29416000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>59014000</v>
+        <v>-17141000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>22898000</v>
-      </c>
+        <v>-5290000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>31144000</v>
-      </c>
+          <t>Total Other Finance Cost</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
       <c r="C33" s="3" t="n">
-        <v>21392000</v>
+        <v>-51847000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>21764000</v>
+        <v>29416000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>16782000</v>
+        <v>-9191000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>19620000</v>
+        <v>9343000</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>176000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Selling And Marketing Expense</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2364000</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>1284000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>1626000</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>1393000</v>
-      </c>
+        <v>29516000</v>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
-        <v>1952000</v>
-      </c>
+        <v>5290000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>28780000</v>
+        <v>-105932000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>20108000</v>
+        <v>-78831000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>20138000</v>
+        <v>6858000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>15389000</v>
+        <v>-24900000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>17668000</v>
-      </c>
+        <v>-98466000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>28780000</v>
+        <v>66891000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>20108000</v>
+        <v>89401000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>20138000</v>
+        <v>33969000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>15389000</v>
+        <v>37720000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>17668000</v>
-      </c>
+        <v>94496000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>10570000</v>
+        <v>19207000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>40827000</v>
+        <v>23060000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12820000</v>
+        <v>-26511000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-3225000</v>
+        <v>-4621000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5099000</v>
-      </c>
+        <v>18823000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Research And Development</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>214265000</v>
+        <v>20199000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>128881000</v>
+        <v>35197000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>142762000</v>
+        <v>39088000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>73353000</v>
+        <v>20577000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>63919000</v>
-      </c>
+        <v>59004000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>224835000</v>
+        <v>27485000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>169708000</v>
+        <v>31144000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>155582000</v>
+        <v>21392000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>70128000</v>
+        <v>21764000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>69018000</v>
-      </c>
+        <v>16669000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2893000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2364000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1284000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1626000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1391000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>24592000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>28780000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>20108000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>15278000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Gand A</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>24592000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>28780000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>20108000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>15278000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-39041000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>10570000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>40827000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>12820000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>-3970000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>227971000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>214265000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>128881000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>142762000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>74098000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>188930000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>224835000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>169708000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>155582000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>70128000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B46" s="3" t="n">
+        <v>188930000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>224835000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>169708000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>155582000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>70128000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>69018000</v>
-      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4562,7 +5189,2027 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n">
+        <v>3364711</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>145762</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>145762</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>145762</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>145762</v>
+      </c>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>235552084</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>235552084</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>221744489</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>211716523</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>196745449</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>235552084</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>238916795</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>221890251</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>211862285</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>196891211</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1659347000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>851739000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>628011000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>233284000</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2028668000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1099297000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>915954000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>625718000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>301177000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>606431000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>738598000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>438852000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>587740000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>680528000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2650223000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1868939000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1398074000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1239827000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1010085000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>706037000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-134015000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-147147000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>33285000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>198080000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>606431000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>738598000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>438852000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>587740000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>680528000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>108560000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>98206000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>91691000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>92642000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>85741000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>730115000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>867848000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>573811000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>706751000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>794649000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2106352000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1115147000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>835910000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>790143000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>794649000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>730115000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>867848000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>573811000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>706751000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>794649000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>730115000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>867848000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>573811000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>706751000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>794649000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>636000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1776852000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1518367000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1384622000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1215245000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>636000</v>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>325597000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>290607000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>290607000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>181065000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-693683000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-583407000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-653949000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-387264000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-239531000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1423162000</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2370976000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1936724000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1863268000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1334319000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>803976000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1538926000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>416062000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>427551000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>252284000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>92851000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n">
+        <v>144378000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>2413000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2489000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2401000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1786000</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>73896000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>77370000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>79400000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>81816000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>84170000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>61420000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>63255000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>65130000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>67006000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>68449000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>12476000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>14115000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>14270000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>14810000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>15721000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1462580000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>336279000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>345662000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>168067000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>6895000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>86343000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>88980000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>83563000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>84675000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>6895000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1376237000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>247299000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>262099000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>83392000</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n">
+        <v>92693000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>832050000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1520662000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1435717000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1082035000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>711125000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>501085000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>672511000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>437953000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>256775000</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>763939000</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>57639000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>64391000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>52512000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>56863000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>61016000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>57639000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>64391000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>52512000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>56863000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>61016000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>566088000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>763018000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>570292000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>457651000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>294282000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>22217000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>9226000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>8128000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>7967000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>78846000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>543871000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>753792000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>562164000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>449684000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>215436000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>543871000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>753792000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>562164000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>449684000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>215436000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>208323000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>192168000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>140402000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>129568000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>99052000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>208323000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>192168000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>140402000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>129568000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>99052000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>57853000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>54655000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>50254000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>39219000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>38098000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>4126000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4340000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>3535000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>11337000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>7788000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>12764000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>13355000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>8564000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2764000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2437000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>12764000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>13355000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>8564000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2764000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2437000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>133580000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>119818000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>78049000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>76248000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>50729000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>3101091000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2804572000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2437079000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2041070000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1598625000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1563004000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1417925000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1148509000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>925750000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>689420000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>51914000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>30840000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>34664000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>79674000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>52558000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>12997000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>11087000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>8333000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>8610000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>8543000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>12997000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>11087000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>8333000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>8610000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>8543000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>31857000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>37876000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>39309000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>40770000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>35083000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>39309000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>40770000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>35083000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>37981000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Financial Assets Designatedas Fair Value Through Profitor Loss Total</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>39309000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>40770000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>35083000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>37981000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Investment Properties</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>29826000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>30098000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>31137000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>30529000</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>30723000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>123684000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>129250000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>134959000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>119011000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>114121000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>87866000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>93432000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>99141000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>83193000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>78303000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>35818000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>35818000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>35818000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>35818000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>35818000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1336533000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1145756000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>899685000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>652235000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>479129000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v>-396156000</v>
+      </c>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n">
+        <v>-288655000</v>
+      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n">
+        <v>-257450000</v>
+      </c>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1336533000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1541912000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>899685000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>940890000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>479129000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>284068000</v>
+      </c>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n">
+        <v>234454000</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>189615000</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>135787000</v>
+      </c>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n">
+        <v>167417000</v>
+      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>144098000</v>
+      </c>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1336533000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>95861000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>493341000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>56338000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>377548000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>124436000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>406344000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>83827000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>101581000</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>49933000</v>
+      </c>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>67649000</v>
+      </c>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n">
+        <v>51235000</v>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>28768000</v>
+      </c>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n">
+        <v>6620000</v>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n">
+        <v>6619000</v>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>3133000</v>
+      </c>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>827491000</v>
+      </c>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>184905000</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1538087000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1386647000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1288570000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1115320000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>909205000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>376225000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>698291000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>564747000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>391633000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>335071000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>30582000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>22366000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>14711000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>12965000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>12107000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>613042000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>251999000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>231544000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>208782000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>153740000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>5417000</v>
+      </c>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n">
+        <v>3542000</v>
+      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>9950000</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n">
+        <v>128182000</v>
+      </c>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n">
+        <v>125445000</v>
+      </c>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n">
+        <v>26277000</v>
+      </c>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n">
+        <v>118400000</v>
+      </c>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n">
+        <v>79795000</v>
+      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n">
+        <v>28661000</v>
+      </c>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>252783000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>176586000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>192984000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>28268000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>26073000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>209867000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>135558000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>163937000</v>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>9635000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>9654000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>11419000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>15568000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>15810000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>33281000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>31374000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>17628000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>10263000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>265455000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>237405000</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>284584000</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>473672000</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>382214000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>4694000</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>88053000</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>88332000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>173880000</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>166572000</v>
+      </c>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>260761000</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>149352000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>196252000</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>299792000</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>215642000</v>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n"/>
+      <c r="C86" s="3" t="n">
+        <v>149352000</v>
+      </c>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n">
+        <v>476270000</v>
+      </c>
+      <c r="H86" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5968,13 +8615,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5984,6 +8631,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5994,30 +8642,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6030,21 +8683,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-440640000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-650267000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-580030000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-446362000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-351583000</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>-373441000</v>
+        <v>-352869000</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6053,21 +8707,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-35000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-9000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-21010000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6076,21 +8731,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-178046000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-25473000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-50185000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-42821000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-1942000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>-16540000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6099,21 +8755,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>176000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>556480000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>346000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>561783000</v>
       </c>
-      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>387917000</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>166297000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6122,21 +8779,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>27761000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>141530000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>91414000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>118403000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>321918000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6145,21 +8803,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-93746000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-50730000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-59748000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-111491000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-67595000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-48383000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6168,21 +8827,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>297694000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>149352000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>196252000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>299792000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>215642000</v>
-      </c>
       <c r="F8" s="3" t="n">
-        <v>476270000</v>
+        <v>233654000</v>
       </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6191,21 +8851,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>866000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>196252000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>299792000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>215642000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>476270000</v>
-      </c>
       <c r="F9" s="3" t="n">
-        <v>291314000</v>
+        <v>2101000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6214,21 +8875,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>177877000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>304000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1342000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>154000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>2101000</v>
-      </c>
       <c r="F10" s="3" t="n">
-        <v>-2801000</v>
+        <v>493626000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6237,21 +8899,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>118951000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-47204000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-104882000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>83996000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>-262729000</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>187757000</v>
+        <v>-262073000</v>
       </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6260,21 +8923,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>352574000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>454453000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>388197000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>431490000</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>94862000</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>522775000</v>
+        <v>96804000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6283,21 +8947,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>352574000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>454453000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>388197000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>431490000</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>94862000</v>
-      </c>
       <c r="F13" s="3" t="n">
-        <v>522775000</v>
+        <v>96804000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6305,18 +8970,21 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>330789000</v>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
         <v>-714000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-129607000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-1119000</v>
       </c>
-      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6325,21 +8993,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>129777000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1682000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-78472000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>530000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>4412000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6348,21 +9017,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>23761000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>106530000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>91414000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-9000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>97393000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>321918000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6371,21 +9041,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-35000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-9000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-21010000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6394,21 +9065,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>27761000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>141530000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>91414000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>118403000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>321918000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6417,21 +9089,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-2046000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>531007000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>295815000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>517843000</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>-1942000</v>
-      </c>
       <c r="F19" s="3" t="n">
-        <v>371377000</v>
+        <v>0</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6440,21 +9113,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-2046000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>531007000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>295815000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>517843000</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>-1942000</v>
-      </c>
       <c r="F20" s="3" t="n">
-        <v>371377000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6463,21 +9137,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-178046000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-25473000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-50185000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-42821000</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>-1942000</v>
-      </c>
       <c r="F21" s="3" t="n">
-        <v>-16540000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6486,21 +9161,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>176000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>556480000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>346000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>561783000</v>
       </c>
-      <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>387917000</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>166297000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6509,21 +9185,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>113271000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>97880000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>27203000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-12623000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-73603000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-9960000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6532,21 +9209,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>113271000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>97880000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>27203000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-12623000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-73603000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-9960000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6554,22 +9232,23 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
         <v>150634000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>89021000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>100068000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-5876000</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>38794000</v>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6578,21 +9257,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>206443000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-2024000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-2070000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-1200000</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>-132000</v>
-      </c>
       <c r="F26" s="3" t="n">
-        <v>-425000</v>
+        <v>-6008000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6600,14 +9280,19 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>206843000</v>
+      </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
+        <v>12283000</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="H27" s="3" t="n">
         <v>173000</v>
       </c>
     </row>
@@ -6618,21 +9303,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-2024000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-2070000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-1200000</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>-132000</v>
-      </c>
       <c r="F28" s="3" t="n">
-        <v>-425000</v>
+        <v>-18291000</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6640,20 +9326,21 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>226000</v>
       </c>
     </row>
@@ -6668,7 +9355,8 @@
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n">
         <v>226000</v>
       </c>
     </row>
@@ -6678,20 +9366,21 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B31" s="3" t="n"/>
       <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6703,10 +9392,11 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
         <v>38794000</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>39929000</v>
       </c>
     </row>
@@ -6720,10 +9410,11 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
         <v>38794000</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
         <v>39929000</v>
       </c>
     </row>
@@ -6734,21 +9425,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-93172000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-50730000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-59748000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-111491000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-67595000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-48329000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6757,7 +9449,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>574000</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -6765,13 +9457,14 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="3" t="n"/>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="3" t="n">
-        <v>54000</v>
-      </c>
-      <c r="G35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6780,21 +9473,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-93746000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-50730000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-59748000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-111491000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-67595000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-48383000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6803,21 +9497,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-346894000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-599537000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-520282000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-334871000</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>-283988000</v>
-      </c>
       <c r="F37" s="3" t="n">
-        <v>-325058000</v>
+        <v>-285274000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6825,22 +9520,23 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
         <v>-599537000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-520282000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-334871000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-283988000</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="G38" s="3" t="n">
         <v>-325058000</v>
       </c>
-      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6848,22 +9544,23 @@
           <t>Taxes Refund Paid</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
         <v>144000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-56000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-502000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-628000</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="G39" s="3" t="n">
         <v>-1964000</v>
       </c>
-      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6871,22 +9568,23 @@
           <t>Interest Received Cfo</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
         <v>1964000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1360000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1749000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>2724000</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="G40" s="3" t="n">
         <v>1653000</v>
       </c>
-      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6894,22 +9592,23 @@
           <t>Interest Paid Cfo</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
         <v>-36172000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-10421000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-16565000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-5195000</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>-3118000</v>
       </c>
-      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6917,29 +9616,30 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
         <v>674693000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-511165000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-319553000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-280889000</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>-22113000</v>
       </c>
-      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
